--- a/data/ARU-PremiumCalc.xlsx
+++ b/data/ARU-PremiumCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\NAGPremCalc\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E2BA5B-2866-4B37-A0DD-C614E655AD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1FE4A9-78AF-4A18-8EA5-F4638620FBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="594" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="594" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="330">
   <si>
     <t>Purpose</t>
   </si>
@@ -399,48 +399,6 @@
     <t>NULL</t>
   </si>
   <si>
-    <t>AFL 90,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3A</t>
-  </si>
-  <si>
-    <t>AFL 150,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3B</t>
-  </si>
-  <si>
-    <t>AFL 200,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3C</t>
-  </si>
-  <si>
-    <t>AFL 250,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3D</t>
-  </si>
-  <si>
-    <t>AFL 300,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3E</t>
-  </si>
-  <si>
-    <t>AFL 500,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C3F</t>
-  </si>
-  <si>
-    <t>AFL 1,000,000.00</t>
-  </si>
-  <si>
-    <t>0x00000000001F8C40</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
@@ -450,69 +408,6 @@
     <t>AFL.</t>
   </si>
   <si>
-    <t>0x000000000018B893</t>
-  </si>
-  <si>
-    <t>0x000000000018B894</t>
-  </si>
-  <si>
-    <t>0x000000000018B895</t>
-  </si>
-  <si>
-    <t>0x000000000018B896</t>
-  </si>
-  <si>
-    <t>0x000000000018B897</t>
-  </si>
-  <si>
-    <t>0x000000000018B898</t>
-  </si>
-  <si>
-    <t>0x000000000018B899</t>
-  </si>
-  <si>
-    <t>0x000000000018B89A</t>
-  </si>
-  <si>
-    <t>0x000000000018B89B</t>
-  </si>
-  <si>
-    <t>0x000000000018B89C</t>
-  </si>
-  <si>
-    <t>0x000000000018B89D</t>
-  </si>
-  <si>
-    <t>0x000000000018B89E</t>
-  </si>
-  <si>
-    <t>0x000000000018B89F</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A0</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A1</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A2</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A3</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A4</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A5</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A6</t>
-  </si>
-  <si>
-    <t>0x000000000018B8A7</t>
-  </si>
-  <si>
     <t>Car</t>
   </si>
   <si>
@@ -997,12 +892,144 @@
   </si>
   <si>
     <t>0x00000000261C591A</t>
+  </si>
+  <si>
+    <t>0x000000001D113B38</t>
+  </si>
+  <si>
+    <t>0x000000001D113B59</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5A</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5B</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5C</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5D</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5E</t>
+  </si>
+  <si>
+    <t>0x000000001D113B5F</t>
+  </si>
+  <si>
+    <t>0x000000001D113B60</t>
+  </si>
+  <si>
+    <t>0x000000001D113B61</t>
+  </si>
+  <si>
+    <t>0x000000001D113B62</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAA</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAB</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAC</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAD</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAE</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EAF</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB0</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB1</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB2</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB3</t>
+  </si>
+  <si>
+    <t>0x000000001D113B6D</t>
+  </si>
+  <si>
+    <t>0x000000001D113B56</t>
+  </si>
+  <si>
+    <t>0x000000001D113B57</t>
+  </si>
+  <si>
+    <t>0x000000001D113B58</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB4</t>
+  </si>
+  <si>
+    <t>0x00000000249B2EB5</t>
+  </si>
+  <si>
+    <t>0x0000000056FAA5F7</t>
+  </si>
+  <si>
+    <t>0x0000000056FAACD2</t>
+  </si>
+  <si>
+    <t>0x0000000056FAACFA</t>
+  </si>
+  <si>
+    <t>0x0000000056FAAD03</t>
+  </si>
+  <si>
+    <t>AFL. 150,000.00</t>
+  </si>
+  <si>
+    <t>0x000000001D113B72</t>
+  </si>
+  <si>
+    <t>AFL. 200,000.00</t>
+  </si>
+  <si>
+    <t>0x000000000026F698</t>
+  </si>
+  <si>
+    <t>AFL. 250,000.00</t>
+  </si>
+  <si>
+    <t>0x000000000026F699</t>
+  </si>
+  <si>
+    <t>AFL. 300,000.00</t>
+  </si>
+  <si>
+    <t>0x000000000026F69A</t>
+  </si>
+  <si>
+    <t>AFL. 500,000.00</t>
+  </si>
+  <si>
+    <t>0x000000000026F69B</t>
+  </si>
+  <si>
+    <t>AFL. 1,000,000.00</t>
+  </si>
+  <si>
+    <t>0x000000000026F69C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1436,7 +1463,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1479,11 +1506,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1511,6 +1540,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1965,7 +1995,7 @@
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -1991,7 +2021,7 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -2017,7 +2047,7 @@
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -2043,7 +2073,7 @@
         <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -2069,7 +2099,7 @@
         <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -2095,7 +2125,7 @@
         <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -2121,7 +2151,7 @@
         <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -2147,7 +2177,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -2173,7 +2203,7 @@
         <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -2199,7 +2229,7 @@
         <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -2225,7 +2255,7 @@
         <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -2251,7 +2281,7 @@
         <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -2277,7 +2307,7 @@
         <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -2303,7 +2333,7 @@
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -2329,7 +2359,7 @@
         <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -2355,7 +2385,7 @@
         <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -2381,7 +2411,7 @@
         <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -2407,7 +2437,7 @@
         <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -2433,7 +2463,7 @@
         <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -2459,7 +2489,7 @@
         <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -2485,7 +2515,7 @@
         <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -2511,7 +2541,7 @@
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -2537,7 +2567,7 @@
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -2563,7 +2593,7 @@
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -2589,7 +2619,7 @@
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -2615,7 +2645,7 @@
         <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -2641,7 +2671,7 @@
         <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -2667,7 +2697,7 @@
         <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -2693,7 +2723,7 @@
         <v>19</v>
       </c>
       <c r="H30" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -2719,7 +2749,7 @@
         <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -2745,7 +2775,7 @@
         <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -2771,7 +2801,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
@@ -2797,7 +2827,7 @@
         <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -2823,7 +2853,7 @@
         <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
@@ -2849,7 +2879,7 @@
         <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -2875,7 +2905,7 @@
         <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -2901,7 +2931,7 @@
         <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
@@ -2927,7 +2957,7 @@
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
@@ -2953,7 +2983,7 @@
         <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
@@ -2979,7 +3009,7 @@
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
@@ -3005,7 +3035,7 @@
         <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -3031,7 +3061,7 @@
         <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -3057,7 +3087,7 @@
         <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
@@ -3083,7 +3113,7 @@
         <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3134,7 @@
         <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="C1" t="s">
         <v>66</v>
@@ -3124,7 +3154,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -3138,7 +3168,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -3152,7 +3182,7 @@
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -3166,7 +3196,7 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -3180,7 +3210,7 @@
         <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -3194,7 +3224,7 @@
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -3208,7 +3238,7 @@
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -3222,7 +3252,7 @@
         <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -3236,7 +3266,7 @@
         <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -3244,13 +3274,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -3258,13 +3288,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -3272,13 +3302,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -3286,13 +3316,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3652,7 +3682,7 @@
         <v>121</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
@@ -3660,10 +3690,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="D3">
         <v>0.2</v>
@@ -3702,7 +3732,7 @@
         <v>121</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
@@ -3752,7 +3782,7 @@
         <v>121</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
@@ -3802,7 +3832,7 @@
         <v>121</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
@@ -3852,7 +3882,7 @@
         <v>121</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
@@ -3863,7 +3893,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="D7">
         <v>0.2</v>
@@ -3902,7 +3932,7 @@
         <v>121</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
@@ -3913,7 +3943,7 @@
         <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="D8">
         <v>0.2</v>
@@ -3952,7 +3982,7 @@
         <v>121</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
@@ -3963,7 +3993,7 @@
         <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4002,7 +4032,7 @@
         <v>121</v>
       </c>
       <c r="P9" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
@@ -4010,10 +4040,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4052,7 +4082,7 @@
         <v>121</v>
       </c>
       <c r="P10" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
@@ -4060,10 +4090,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4102,7 +4132,7 @@
         <v>121</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
@@ -4110,10 +4140,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="D12">
         <v>0.2</v>
@@ -4152,7 +4182,7 @@
         <v>121</v>
       </c>
       <c r="P12" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4162,7 +4192,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.07421875" customWidth="1"/>
@@ -4187,121 +4217,104 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>318</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>320</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>322</v>
       </c>
       <c r="C4">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="C5">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8">
-        <v>0.8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +4407,7 @@
         <v>44</v>
       </c>
       <c r="AA1" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
@@ -4474,7 +4487,7 @@
         <v>121</v>
       </c>
       <c r="Z2" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -4557,7 +4570,7 @@
         <v>121</v>
       </c>
       <c r="Z3" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="AA3">
         <v>75</v>
@@ -4565,7 +4578,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B4">
         <v>67</v>
@@ -4640,7 +4653,7 @@
         <v>121</v>
       </c>
       <c r="Z4" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="AA4">
         <v>0</v>
@@ -4648,7 +4661,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4723,7 +4736,7 @@
         <v>121</v>
       </c>
       <c r="Z5" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="AA5">
         <v>75</v>
@@ -4806,7 +4819,7 @@
         <v>121</v>
       </c>
       <c r="Z6" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -4889,7 +4902,7 @@
         <v>121</v>
       </c>
       <c r="Z7" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="AA7">
         <v>75</v>
@@ -4972,7 +4985,7 @@
         <v>121</v>
       </c>
       <c r="Z8" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AA8">
         <v>0</v>
@@ -5055,7 +5068,7 @@
         <v>121</v>
       </c>
       <c r="Z9" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="AA9">
         <v>75</v>
@@ -5138,7 +5151,7 @@
         <v>121</v>
       </c>
       <c r="Z10" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="AA10">
         <v>0</v>
@@ -5221,7 +5234,7 @@
         <v>121</v>
       </c>
       <c r="Z11" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="AA11">
         <v>75</v>
@@ -5304,7 +5317,7 @@
         <v>121</v>
       </c>
       <c r="Z12" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="AA12">
         <v>0</v>
@@ -5387,7 +5400,7 @@
         <v>121</v>
       </c>
       <c r="Z13" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="AA13">
         <v>75</v>
@@ -5395,7 +5408,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5470,7 +5483,7 @@
         <v>121</v>
       </c>
       <c r="Z14" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="AA14">
         <v>75</v>
@@ -5553,7 +5566,7 @@
         <v>121</v>
       </c>
       <c r="Z15" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="AA15">
         <v>0</v>
@@ -5636,7 +5649,7 @@
         <v>121</v>
       </c>
       <c r="Z16" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="AA16">
         <v>75</v>
@@ -5719,7 +5732,7 @@
         <v>121</v>
       </c>
       <c r="Z17" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AA17">
         <v>0</v>
@@ -5802,7 +5815,7 @@
         <v>121</v>
       </c>
       <c r="Z18" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="AA18">
         <v>75</v>
@@ -5885,7 +5898,7 @@
         <v>121</v>
       </c>
       <c r="Z19" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="AA19">
         <v>75</v>
@@ -5893,7 +5906,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B20">
         <v>67</v>
@@ -5968,7 +5981,7 @@
         <v>121</v>
       </c>
       <c r="Z20" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="AA20">
         <v>75</v>
@@ -6051,7 +6064,7 @@
         <v>121</v>
       </c>
       <c r="Z21" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="AA21">
         <v>75</v>
@@ -6134,7 +6147,7 @@
         <v>121</v>
       </c>
       <c r="Z22" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="AA22">
         <v>75</v>
@@ -6217,7 +6230,7 @@
         <v>121</v>
       </c>
       <c r="Z23" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="AA23">
         <v>75</v>
@@ -6300,7 +6313,7 @@
         <v>121</v>
       </c>
       <c r="Z24" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="AA24">
         <v>75</v>
@@ -6383,7 +6396,7 @@
         <v>121</v>
       </c>
       <c r="Z25" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="AA25">
         <v>75</v>
@@ -6466,7 +6479,7 @@
         <v>121</v>
       </c>
       <c r="Z26" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="AA26">
         <v>75</v>
@@ -6474,7 +6487,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6528,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="T27" t="s">
         <v>19</v>
@@ -6549,7 +6562,7 @@
         <v>121</v>
       </c>
       <c r="Z27" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="AA27">
         <v>0</v>
@@ -6557,7 +6570,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B28">
         <v>67</v>
@@ -6632,7 +6645,7 @@
         <v>121</v>
       </c>
       <c r="Z28" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -6640,7 +6653,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6715,7 +6728,7 @@
         <v>121</v>
       </c>
       <c r="Z29" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="AA29">
         <v>75</v>
@@ -6798,7 +6811,7 @@
         <v>121</v>
       </c>
       <c r="Z30" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -6806,7 +6819,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B31">
         <v>67</v>
@@ -6881,7 +6894,7 @@
         <v>121</v>
       </c>
       <c r="Z31" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -6964,7 +6977,7 @@
         <v>121</v>
       </c>
       <c r="Z32" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="AA32">
         <v>0</v>
@@ -7047,7 +7060,7 @@
         <v>121</v>
       </c>
       <c r="Z33" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -7130,7 +7143,7 @@
         <v>121</v>
       </c>
       <c r="Z34" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="AA34">
         <v>0</v>
@@ -7213,7 +7226,7 @@
         <v>121</v>
       </c>
       <c r="Z35" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="AA35">
         <v>0</v>
@@ -7296,7 +7309,7 @@
         <v>121</v>
       </c>
       <c r="Z36" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="AA36">
         <v>0</v>
@@ -7379,7 +7392,7 @@
         <v>121</v>
       </c>
       <c r="Z37" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -7387,7 +7400,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B38">
         <v>67</v>
@@ -7462,7 +7475,7 @@
         <v>121</v>
       </c>
       <c r="Z38" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="AA38">
         <v>0</v>
@@ -7470,7 +7483,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B39">
         <v>67</v>
@@ -7545,7 +7558,7 @@
         <v>121</v>
       </c>
       <c r="Z39" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="AA39">
         <v>75</v>
@@ -7628,7 +7641,7 @@
         <v>121</v>
       </c>
       <c r="Z40" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="AA40">
         <v>0</v>
@@ -7641,8 +7654,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="4" max="4" width="11.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -7654,10 +7671,10 @@
       <c r="C1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>89</v>
       </c>
       <c r="F1" t="s">
@@ -7695,20 +7712,20 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>25000</v>
+      <c r="E2" s="1">
+        <v>5000</v>
       </c>
       <c r="F2" t="s">
         <v>121</v>
       </c>
       <c r="G2">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s">
         <v>121</v>
@@ -7723,7 +7740,7 @@
         <v>121</v>
       </c>
       <c r="M2" t="s">
-        <v>139</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -7734,22 +7751,22 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1">
         <v>25001</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>30000</v>
       </c>
       <c r="F3" t="s">
         <v>121</v>
       </c>
       <c r="G3">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="H3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
         <v>121</v>
@@ -7764,7 +7781,7 @@
         <v>121</v>
       </c>
       <c r="M3" t="s">
-        <v>140</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -7775,22 +7792,22 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
         <v>30001</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>35000</v>
       </c>
       <c r="F4" t="s">
         <v>121</v>
       </c>
       <c r="G4">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s">
         <v>121</v>
@@ -7805,7 +7822,7 @@
         <v>121</v>
       </c>
       <c r="M4" t="s">
-        <v>141</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -7816,22 +7833,22 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
         <v>35001</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>40000</v>
       </c>
       <c r="F5" t="s">
         <v>121</v>
       </c>
       <c r="G5">
-        <v>664</v>
+        <v>704</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s">
         <v>121</v>
@@ -7846,7 +7863,7 @@
         <v>121</v>
       </c>
       <c r="M5" t="s">
-        <v>142</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -7857,22 +7874,22 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
         <v>40001</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45000</v>
       </c>
       <c r="F6" t="s">
         <v>121</v>
       </c>
       <c r="G6">
-        <v>704</v>
+        <v>746</v>
       </c>
       <c r="H6" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I6" t="s">
         <v>121</v>
@@ -7887,7 +7904,7 @@
         <v>121</v>
       </c>
       <c r="M6" t="s">
-        <v>143</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -7898,22 +7915,22 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
         <v>45001</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>50000</v>
       </c>
       <c r="F7" t="s">
         <v>121</v>
       </c>
       <c r="G7">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="H7" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I7" t="s">
         <v>121</v>
@@ -7928,7 +7945,7 @@
         <v>121</v>
       </c>
       <c r="M7" t="s">
-        <v>144</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -7939,22 +7956,22 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
         <v>50001</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>55000</v>
       </c>
       <c r="F8" t="s">
         <v>121</v>
       </c>
       <c r="G8">
-        <v>869</v>
+        <v>921</v>
       </c>
       <c r="H8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I8" t="s">
         <v>121</v>
@@ -7969,7 +7986,7 @@
         <v>121</v>
       </c>
       <c r="M8" t="s">
-        <v>145</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -7980,22 +7997,22 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1">
         <v>55001</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>60000</v>
       </c>
       <c r="F9" t="s">
         <v>121</v>
       </c>
       <c r="G9">
-        <v>952</v>
+        <v>1009</v>
       </c>
       <c r="H9" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I9" t="s">
         <v>121</v>
@@ -8010,7 +8027,7 @@
         <v>121</v>
       </c>
       <c r="M9" t="s">
-        <v>146</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -8021,22 +8038,22 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1">
         <v>60001</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>65000</v>
       </c>
       <c r="F10" t="s">
         <v>121</v>
       </c>
       <c r="G10">
-        <v>1034</v>
+        <v>1096</v>
       </c>
       <c r="H10" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s">
         <v>121</v>
@@ -8051,7 +8068,7 @@
         <v>121</v>
       </c>
       <c r="M10" t="s">
-        <v>147</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -8062,22 +8079,22 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1">
         <v>65001</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>70000</v>
       </c>
       <c r="F11" t="s">
         <v>121</v>
       </c>
       <c r="G11">
-        <v>1117</v>
+        <v>1184</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
         <v>121</v>
@@ -8092,7 +8109,7 @@
         <v>121</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -8103,22 +8120,22 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1">
         <v>70001</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>75000</v>
       </c>
       <c r="F12" t="s">
         <v>121</v>
       </c>
       <c r="G12">
-        <v>1199</v>
+        <v>1271</v>
       </c>
       <c r="H12" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I12" t="s">
         <v>121</v>
@@ -8133,7 +8150,7 @@
         <v>121</v>
       </c>
       <c r="M12" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -8144,22 +8161,22 @@
         <v>19</v>
       </c>
       <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1">
         <v>75001</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>80000</v>
       </c>
       <c r="F13" t="s">
         <v>121</v>
       </c>
       <c r="G13">
-        <v>1282</v>
+        <v>1271</v>
       </c>
       <c r="H13" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
         <v>121</v>
@@ -8174,7 +8191,7 @@
         <v>121</v>
       </c>
       <c r="M13" t="s">
-        <v>150</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -8185,22 +8202,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>13</v>
-      </c>
-      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1">
         <v>80001</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>85000</v>
       </c>
       <c r="F14" t="s">
         <v>121</v>
       </c>
       <c r="G14">
-        <v>1364</v>
+        <v>1271</v>
       </c>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I14" t="s">
         <v>121</v>
@@ -8215,7 +8232,7 @@
         <v>121</v>
       </c>
       <c r="M14" t="s">
-        <v>151</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -8226,22 +8243,22 @@
         <v>19</v>
       </c>
       <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1">
         <v>85001</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>90000</v>
       </c>
       <c r="F15" t="s">
         <v>121</v>
       </c>
       <c r="G15">
-        <v>1447</v>
+        <v>1271</v>
       </c>
       <c r="H15" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s">
         <v>121</v>
@@ -8256,7 +8273,7 @@
         <v>121</v>
       </c>
       <c r="M15" t="s">
-        <v>152</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -8267,22 +8284,22 @@
         <v>19</v>
       </c>
       <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="D16">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1">
         <v>90001</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>95000</v>
       </c>
       <c r="F16" t="s">
         <v>121</v>
       </c>
       <c r="G16">
-        <v>1529</v>
+        <v>1271</v>
       </c>
       <c r="H16" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s">
         <v>121</v>
@@ -8297,7 +8314,7 @@
         <v>121</v>
       </c>
       <c r="M16" t="s">
-        <v>153</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -8308,22 +8325,22 @@
         <v>19</v>
       </c>
       <c r="C17">
-        <v>16</v>
-      </c>
-      <c r="D17">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1">
         <v>95001</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>100000</v>
       </c>
       <c r="F17" t="s">
         <v>121</v>
       </c>
       <c r="G17">
-        <v>1612</v>
+        <v>1271</v>
       </c>
       <c r="H17" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I17" t="s">
         <v>121</v>
@@ -8338,7 +8355,7 @@
         <v>121</v>
       </c>
       <c r="M17" t="s">
-        <v>154</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -8349,22 +8366,22 @@
         <v>19</v>
       </c>
       <c r="C18">
-        <v>16</v>
-      </c>
-      <c r="D18">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1">
         <v>100001</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>105000</v>
       </c>
       <c r="F18" t="s">
         <v>121</v>
       </c>
       <c r="G18">
-        <v>1694</v>
+        <v>1271</v>
       </c>
       <c r="H18" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I18" t="s">
         <v>121</v>
@@ -8379,7 +8396,7 @@
         <v>121</v>
       </c>
       <c r="M18" t="s">
-        <v>155</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -8390,22 +8407,22 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>18</v>
-      </c>
-      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1">
         <v>105001</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>110000</v>
       </c>
       <c r="F19" t="s">
         <v>121</v>
       </c>
       <c r="G19">
-        <v>1777</v>
+        <v>1271</v>
       </c>
       <c r="H19" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I19" t="s">
         <v>121</v>
@@ -8420,7 +8437,7 @@
         <v>121</v>
       </c>
       <c r="M19" t="s">
-        <v>156</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -8431,22 +8448,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>19</v>
-      </c>
-      <c r="D20">
+        <v>26</v>
+      </c>
+      <c r="D20" s="1">
         <v>110001</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>115000</v>
       </c>
       <c r="F20" t="s">
         <v>121</v>
       </c>
       <c r="G20">
-        <v>1859</v>
+        <v>1271</v>
       </c>
       <c r="H20" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I20" t="s">
         <v>121</v>
@@ -8461,7 +8478,7 @@
         <v>121</v>
       </c>
       <c r="M20" t="s">
-        <v>157</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -8472,22 +8489,22 @@
         <v>19</v>
       </c>
       <c r="C21">
-        <v>20</v>
-      </c>
-      <c r="D21">
+        <v>27</v>
+      </c>
+      <c r="D21" s="1">
         <v>115001</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>120000</v>
       </c>
       <c r="F21" t="s">
         <v>121</v>
       </c>
       <c r="G21">
-        <v>1942</v>
+        <v>1271</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I21" t="s">
         <v>121</v>
@@ -8502,7 +8519,7 @@
         <v>121</v>
       </c>
       <c r="M21" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -8513,37 +8530,447 @@
         <v>19</v>
       </c>
       <c r="C22">
-        <v>21</v>
-      </c>
-      <c r="D22">
+        <v>28</v>
+      </c>
+      <c r="D22" s="1">
         <v>120001</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
+        <v>125000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22">
+        <v>1271</v>
+      </c>
+      <c r="H22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" t="s">
+        <v>121</v>
+      </c>
+      <c r="J22" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" t="s">
+        <v>121</v>
+      </c>
+      <c r="L22" t="s">
+        <v>121</v>
+      </c>
+      <c r="M22" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5001</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23">
+        <v>330</v>
+      </c>
+      <c r="H23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J23" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" t="s">
+        <v>121</v>
+      </c>
+      <c r="L23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M23" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E24" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24">
+        <v>379</v>
+      </c>
+      <c r="H24" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24" t="s">
+        <v>121</v>
+      </c>
+      <c r="L24" t="s">
+        <v>121</v>
+      </c>
+      <c r="M24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1">
+        <v>15001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25">
+        <v>427</v>
+      </c>
+      <c r="H25" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" t="s">
+        <v>121</v>
+      </c>
+      <c r="J25" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" t="s">
+        <v>121</v>
+      </c>
+      <c r="L25" t="s">
+        <v>121</v>
+      </c>
+      <c r="M25" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1">
+        <v>20001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26">
+        <v>509</v>
+      </c>
+      <c r="H26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" t="s">
+        <v>121</v>
+      </c>
+      <c r="L26" t="s">
+        <v>121</v>
+      </c>
+      <c r="M26" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1">
+        <v>125001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>130000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27">
+        <v>1271</v>
+      </c>
+      <c r="H27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" t="s">
+        <v>121</v>
+      </c>
+      <c r="J27" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L27" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28" s="1">
+        <v>130001</v>
+      </c>
+      <c r="E28" s="1">
         <v>1000000</v>
       </c>
-      <c r="F22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G22">
-        <v>2024</v>
-      </c>
-      <c r="H22" t="s">
-        <v>138</v>
-      </c>
-      <c r="I22" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" t="s">
-        <v>121</v>
-      </c>
-      <c r="K22" t="s">
-        <v>121</v>
-      </c>
-      <c r="L22" t="s">
-        <v>121</v>
-      </c>
-      <c r="M22" t="s">
-        <v>159</v>
+      <c r="F28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28">
+        <v>1271</v>
+      </c>
+      <c r="H28" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" t="s">
+        <v>121</v>
+      </c>
+      <c r="J28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28" t="s">
+        <v>121</v>
+      </c>
+      <c r="L28" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>31</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29">
+        <v>635.14</v>
+      </c>
+      <c r="H29" t="s">
+        <v>124</v>
+      </c>
+      <c r="I29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>32</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3001</v>
+      </c>
+      <c r="E30" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30">
+        <v>725.23</v>
+      </c>
+      <c r="H30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K30" t="s">
+        <v>121</v>
+      </c>
+      <c r="L30" t="s">
+        <v>121</v>
+      </c>
+      <c r="M30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>33</v>
+      </c>
+      <c r="D31" s="1">
+        <v>4501</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31">
+        <v>792.79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <v>34</v>
+      </c>
+      <c r="D32" s="1">
+        <v>6001</v>
+      </c>
+      <c r="E32" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F32" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32">
+        <v>860.36</v>
+      </c>
+      <c r="H32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" t="s">
+        <v>121</v>
+      </c>
+      <c r="L32" t="s">
+        <v>121</v>
+      </c>
+      <c r="M32" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -8578,7 +9005,7 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -8592,7 +9019,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -8684,7 +9111,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -8692,7 +9119,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -8700,7 +9127,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8715,7 +9142,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="B1" t="s">
         <v>46</v>
@@ -8724,34 +9151,34 @@
         <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="E1" t="s">
         <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="H1" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="I1" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="J1" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="K1" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="L1" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="M1" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="N1" t="s">
         <v>44</v>
@@ -8768,10 +9195,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
         <v>121</v>
@@ -8798,7 +9225,7 @@
         <v>121</v>
       </c>
       <c r="N2" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -8812,10 +9239,10 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
         <v>121</v>
@@ -8842,7 +9269,7 @@
         <v>121</v>
       </c>
       <c r="N3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -8856,10 +9283,10 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
         <v>121</v>
@@ -8886,7 +9313,7 @@
         <v>121</v>
       </c>
       <c r="N4" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -8900,10 +9327,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
         <v>121</v>
@@ -8930,7 +9357,7 @@
         <v>121</v>
       </c>
       <c r="N5" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -8944,10 +9371,10 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
         <v>121</v>
@@ -8974,7 +9401,7 @@
         <v>121</v>
       </c>
       <c r="N6" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
@@ -8988,10 +9415,10 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F7" t="s">
         <v>121</v>
@@ -9018,7 +9445,7 @@
         <v>121</v>
       </c>
       <c r="N7" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
@@ -9032,10 +9459,10 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
         <v>121</v>
@@ -9062,7 +9489,7 @@
         <v>121</v>
       </c>
       <c r="N8" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
@@ -9076,10 +9503,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
         <v>121</v>
@@ -9106,7 +9533,7 @@
         <v>121</v>
       </c>
       <c r="N9" t="s">
-        <v>313</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
@@ -9120,10 +9547,10 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
         <v>121</v>
@@ -9150,7 +9577,7 @@
         <v>121</v>
       </c>
       <c r="N10" t="s">
-        <v>315</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
@@ -9164,10 +9591,10 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F11" t="s">
         <v>121</v>
@@ -9194,7 +9621,7 @@
         <v>121</v>
       </c>
       <c r="N11" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
@@ -9208,10 +9635,10 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
         <v>121</v>
@@ -9238,7 +9665,7 @@
         <v>121</v>
       </c>
       <c r="N12" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
@@ -9252,10 +9679,10 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
         <v>121</v>
@@ -9282,7 +9709,7 @@
         <v>121</v>
       </c>
       <c r="N13" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/data/ARU-PremiumCalc.xlsx
+++ b/data/ARU-PremiumCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\NAGPremCalc\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1FE4A9-78AF-4A18-8EA5-F4638620FBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FA1AA0-0B12-4185-A9AA-0FBF49644E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="594" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="594" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -3456,6 +3456,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="4" max="4" width="9.3828125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -3514,7 +3517,7 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>0.08</v>
+        <v>8.4000128024580706E-2</v>
       </c>
       <c r="E3">
         <v>80</v>

--- a/data/ARU-PremiumCalc.xlsx
+++ b/data/ARU-PremiumCalc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\NAGPremCalc\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FA1AA0-0B12-4185-A9AA-0FBF49644E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898D61C0-C4CB-4F66-A134-E6E9A0E6CC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="594" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1027,8 +1027,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="174" formatCode="0.0000000000000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1508,9 +1509,10 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3457,7 +3459,7 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="4" max="4" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -3516,7 +3518,7 @@
       <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>8.4000128024580706E-2</v>
       </c>
       <c r="E3">
